--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Mikael Hägg, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Mikael Hägg, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>136980446</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mikael Hägg, Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2703,7 +2703,7 @@
         <v>136980462</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mikael Hägg, Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>136980446</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136980462</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -2616,11 +2616,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2731,11 +2727,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>136980446</v>
       </c>
       <c r="B19" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136980462</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>136980446</v>
       </c>
       <c r="B19" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136980462</v>
       </c>
       <c r="B20" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>136980446</v>
       </c>
       <c r="B19" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136980462</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Mikael Hägg, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Hägg, Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93501</v>
+        <v>93502</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93501</v>
+        <v>93502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92238</v>
+        <v>92239</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Mikael Hägg, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Mikael Hägg, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90967</v>
+        <v>90968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90967</v>
+        <v>90968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26561-2026 artfynd.xlsx
+++ b/artfynd/A 26561-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136980052</v>
       </c>
       <c r="B2" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136980065</v>
       </c>
       <c r="B3" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136980309</v>
       </c>
       <c r="B4" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136980548</v>
       </c>
       <c r="B5" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136980071</v>
       </c>
       <c r="B6" t="n">
-        <v>93502</v>
+        <v>93505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136980208</v>
       </c>
       <c r="B7" t="n">
-        <v>93502</v>
+        <v>93505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136980099</v>
       </c>
       <c r="B8" t="n">
-        <v>92239</v>
+        <v>92242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hägg, Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
         <v>136980261</v>
       </c>
       <c r="B9" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136980272</v>
       </c>
       <c r="B10" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136980284</v>
       </c>
       <c r="B11" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136980558</v>
       </c>
       <c r="B12" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136980090</v>
       </c>
       <c r="B13" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mikael Hägg, Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2033,7 +2033,7 @@
         <v>136980142</v>
       </c>
       <c r="B14" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136980421</v>
       </c>
       <c r="B15" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>136980060</v>
       </c>
       <c r="B16" t="n">
-        <v>90968</v>
+        <v>90971</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136980378</v>
       </c>
       <c r="B17" t="n">
-        <v>90968</v>
+        <v>90971</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136980113</v>
       </c>
       <c r="B18" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>136980446</v>
       </c>
       <c r="B19" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136980462</v>
       </c>
       <c r="B20" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
